--- a/jpcore-r4/feature/add-servicerequest-order-laboratory-item/StructureDefinition-jp-servicerequest-order-laboratory-item.xlsx
+++ b/jpcore-r4/feature/add-servicerequest-order-laboratory-item/StructureDefinition-jp-servicerequest-order-laboratory-item.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$56</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2073" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="517">
   <si>
     <t>Property</t>
   </si>
@@ -866,7 +866,8 @@
     <t>検索、分類、表示の目的でサービスを分類するコード（例 「外科的手技」）</t>
   </si>
   <si>
-    <t>【JP Core仕様】検体検査であることを示す区分を設定する。使用するコード表は個別仕様で定めてよい。</t>
+    <t>【JP Core仕様】このプロファイルでは必須とする。
+検体検査の依頼であることを判別できるよう、laboratory スライスを必ず設定する。施設固有の区分などを追加で設定してもよい。</t>
   </si>
   <si>
     <t>Used for filtering what service request are retrieved and displayed.</t>
@@ -881,10 +882,37 @@
     <t>http://hl7.org/fhir/ValueSet/servicerequest-category|4.0.1</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
     <t>RF1-5</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="INT"].code</t>
+  </si>
+  <si>
+    <t>ServiceRequest.category:laboratory</t>
+  </si>
+  <si>
+    <t>laboratory</t>
+  </si>
+  <si>
+    <t>検体検査を示す区分（laboratory 固定）【詳細参照】</t>
+  </si>
+  <si>
+    <t>検体検査の依頼であることを示す区分。</t>
+  </si>
+  <si>
+    <t>【JP Core仕様】結果として返される Observation（JP_Observation_LabResult）の category と同じコード表（JP Core Simple Observation Category CodeSystem）を使用し、laboratory に固定する。</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS"/&gt;
+    &lt;code value="laboratory"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>ServiceRequest.priority</t>
@@ -970,10 +998,10 @@
 標準コードとして JLAC10（または JLAC11）を使用する。結果として返される Observation（JP_Observation_LabResult）の code と同じコード体系を使用すると、依頼と結果の突合が容易になる。</t>
   </si>
   <si>
-    <t>指定された個人、組織、または医療サービスによって実施できるテストやサービスのコード。ラボの場合、LOINCが（preferred）[http://build.fhir.org/terminologies.html#preferred]であり、LOINCオーダーコードを使用した値セットが[こちら]（valueset-diagnostic-requests.html）で利用可能です。</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
+    <t>MEDIS 臨床検査マスター</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationLabResultCode_VS</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -1016,7 +1044,7 @@
     <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
   </si>
   <si>
-    <t>【JP Core仕様】標準コードとローカルコードの両方を設定できる。いずれか一方は設定すること。JLAC10 と JLAC11 など複数の標準コードを設定できるよう、上限は設けない。</t>
+    <t>【JP Core仕様】このプロファイルでは必須とする。標準コードとローカルコードの両方を設定できる。いずれか一方は設定すること。JLAC10 と JLAC11 など複数の標準コードを設定できるよう、上限は設けない。</t>
   </si>
   <si>
     <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
@@ -1405,13 +1433,14 @@
     <t>ServiceRequest.reasonCode</t>
   </si>
   <si>
-    <t>行為やサービスの説明・理由</t>
-  </si>
-  <si>
-    <t>このサービスがリクエストされる理由についての説明または根拠をコード化またはテキスト化したもの。しばしば（保険）請求を目的とされる。supportingInfoで参照されるリソースに関連する場合がある。</t>
-  </si>
-  <si>
-    <t>この要素は照会理由を表し、サービスがどのように実行されるか、あるいは全く実行されないかどうかを決定するために使用される。CTスキャンの例で示したように、データが自由記述の場合は、CodeableConcept.text要素を使用する。</t>
+    <t>検査目的、依頼病名【詳細参照】</t>
+  </si>
+  <si>
+    <t>検査を依頼する理由。検査目的や依頼病名をコードまたはテキストで表現する。</t>
+  </si>
+  <si>
+    <t>【JP Core仕様】検査目的は自由記載が多いため、text に設定する。依頼病名は、コード化されている場合は coding に、コード化されていない場合は text に設定する。
+病名を Condition リソースとして参照できる場合は reasonReference を使用する。同じ理由を reasonCode と reasonReference の両方に重複して設定しないこと。</t>
   </si>
   <si>
     <t>サービス調査の依頼理由を正当化する診断または問題コード。</t>
@@ -1439,13 +1468,13 @@
 </t>
   </si>
   <si>
-    <t>行為やサービスの説明・理由（参照）</t>
-  </si>
-  <si>
-    <t>このサービスが要求される理由の正当性を提供する他のリソースを示す。supportingInfoで参照されるリソースに関連する場合がある。</t>
-  </si>
-  <si>
-    <t>この要素は照会理由を表し、サービスがどのように実行されるか、あるいは全く実行されないかどうかを決定するために使用される。可能な限り具体的にするために、ObservationやConditionリソースへの参照が可能であれば使用されるべきである。また、DiagnosticReport を参照する場合は、DiagnosticReport.conclusion および/または DiagnosticReport.conclusionCode を参照する必要がある。DocumentReference への参照を使用する場合、ターゲット文書は、このサービス要求の関連理由を提供する明確な所見言語を含んでいなければならない。CTスキャンの例に示すように、データが自由記述（符号化されていない）の場合、 ServiceRequest.reasonCodeにCodeableConcept.text要素を使用する。</t>
+    <t>依頼病名などへの参照【詳細参照】</t>
+  </si>
+  <si>
+    <t>検査を依頼する理由となるリソースへの参照。</t>
+  </si>
+  <si>
+    <t>【JP Core仕様】依頼病名を Condition リソース（JP_Condition）として参照できる場合に使用する。</t>
   </si>
   <si>
     <t>Request.reasonReference</t>
@@ -1496,7 +1525,7 @@
     <t>サービスやその解釈に影響を与える可能性のある、患者や検体に関する追加の臨床情報。この情報には、診断、臨床所見、その他の観察が含まれる。検査のオーダでは、一般的に「オーダエントリー時の質問（AOEs）」と呼ばれ ている。これには、オーダを完了するために必要な文脈や裏付けとなる情報を提供するために、実施者が明示的に要求した観察が含まれる。例えば、血液ガス測定のための吸入酸素量の報告などである。</t>
   </si>
   <si>
-    <t>サービスの提供方法に関する情報を表すには、instructions 要素を使用する。</t>
+    <t>【JP Core仕様】検査の実施や結果の解釈に必要な患者情報（身長、体重、採取時の状態など）を、Observation などのリソースへの参照として設定する。</t>
   </si>
   <si>
     <t>Request.supportingInfo</t>
@@ -1569,10 +1598,13 @@
 </t>
   </si>
   <si>
-    <t>コメント</t>
+    <t>依頼コメント【詳細参照】</t>
   </si>
   <si>
     <t>サービス要求について作成された、その他のメモやコメント。例えば、内部請求のメモなど。</t>
+  </si>
+  <si>
+    <t>【JP Core仕様】検査部門への連絡事項など、他の要素で表現できない依頼コメントをテキストで設定する。</t>
   </si>
   <si>
     <t>Request.note</t>
@@ -1934,7 +1966,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO55"/>
+  <dimension ref="A1:AO56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.62109375" customWidth="true" bestFit="true"/>
@@ -1961,7 +1993,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="166.44140625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="56.54296875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="58.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -5036,7 +5068,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>81</v>
@@ -5100,16 +5132,14 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>267</v>
@@ -5130,10 +5160,10 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>266</v>
@@ -5144,18 +5174,20 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>92</v>
@@ -5170,29 +5202,29 @@
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>165</v>
+        <v>268</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q28" t="s" s="2">
-        <v>282</v>
-      </c>
+      <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>82</v>
@@ -5207,13 +5239,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5231,13 +5263,13 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
@@ -5246,16 +5278,16 @@
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>285</v>
+        <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5263,10 +5295,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5283,59 +5315,57 @@
         <v>82</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q29" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="R29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="Y29" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="Z29" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="M29" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="P29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q29" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="R29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5352,7 +5382,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5367,16 +5397,16 @@
         <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>82</v>
+        <v>295</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5384,18 +5414,18 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>92</v>
@@ -5404,28 +5434,32 @@
         <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="P30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q30" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="O30" s="2"/>
-      <c r="P30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5445,13 +5479,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>304</v>
+        <v>82</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5469,7 +5503,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5484,35 +5518,35 @@
         <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>308</v>
+        <v>82</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>309</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>82</v>
+        <v>306</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>92</v>
@@ -5524,18 +5558,20 @@
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>106</v>
+        <v>268</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>107</v>
+        <v>307</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5560,13 +5596,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -5584,7 +5620,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>109</v>
+        <v>305</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5596,30 +5632,30 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>110</v>
+        <v>314</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>82</v>
+        <v>316</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5630,7 +5666,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5642,13 +5678,13 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>194</v>
+        <v>318</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5687,31 +5723,31 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -5720,7 +5756,7 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
@@ -5731,10 +5767,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5754,23 +5790,19 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>316</v>
+        <v>114</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5806,19 +5838,19 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5836,10 +5868,10 @@
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>322</v>
+        <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>323</v>
+        <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
@@ -5850,10 +5882,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5864,7 +5896,7 @@
         <v>92</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5876,19 +5908,19 @@
         <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -5937,28 +5969,28 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AG34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
@@ -5969,21 +6001,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -5995,18 +6027,20 @@
         <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>268</v>
+        <v>106</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="N35" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6030,77 +6064,77 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="Z35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AA35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>307</v>
-      </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>309</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>82</v>
+        <v>340</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6112,20 +6146,18 @@
         <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M36" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>346</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6149,13 +6181,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6173,16 +6205,16 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>104</v>
@@ -6191,16 +6223,16 @@
         <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>347</v>
+        <v>314</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>82</v>
+        <v>316</v>
       </c>
     </row>
     <row r="37" hidden="true">
@@ -6216,7 +6248,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>92</v>
@@ -6242,7 +6274,9 @@
       <c r="N37" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="O37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6293,7 +6327,7 @@
         <v>348</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>92</v>
@@ -6305,35 +6339,35 @@
         <v>104</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AM37" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AN37" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>92</v>
@@ -6348,16 +6382,16 @@
         <v>93</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6407,10 +6441,10 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>92</v>
@@ -6422,31 +6456,31 @@
         <v>104</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>368</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6465,16 +6499,16 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6524,7 +6558,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6539,31 +6573,31 @@
         <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>379</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6582,15 +6616,17 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="L40" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6615,13 +6651,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>384</v>
+        <v>82</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6639,7 +6675,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6654,31 +6690,31 @@
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>387</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6697,13 +6733,13 @@
         <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6730,13 +6766,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>82</v>
+        <v>392</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -6754,7 +6790,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6769,31 +6805,31 @@
         <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>397</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6812,17 +6848,15 @@
         <v>93</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6871,7 +6905,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6886,31 +6920,31 @@
         <v>104</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>408</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6929,16 +6963,16 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>268</v>
+        <v>407</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6964,13 +6998,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>414</v>
+        <v>82</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>415</v>
+        <v>82</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -6988,7 +7022,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7003,38 +7037,38 @@
         <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7046,16 +7080,16 @@
         <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>422</v>
+        <v>268</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7081,13 +7115,13 @@
         <v>82</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>82</v>
@@ -7105,13 +7139,13 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
@@ -7120,16 +7154,16 @@
         <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7137,14 +7171,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>428</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7163,7 +7197,7 @@
         <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>268</v>
+        <v>429</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>430</v>
@@ -7171,7 +7205,9 @@
       <c r="M45" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="N45" s="2"/>
+      <c r="N45" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7196,13 +7232,13 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7220,7 +7256,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7235,16 +7271,16 @@
         <v>104</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>82</v>
+        <v>434</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7252,10 +7288,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7278,7 +7314,7 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>436</v>
+        <v>268</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>437</v>
@@ -7311,13 +7347,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7335,7 +7371,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7356,10 +7392,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7367,10 +7403,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7393,17 +7429,15 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>268</v>
+        <v>443</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7428,13 +7462,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7452,7 +7486,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7467,16 +7501,16 @@
         <v>104</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AL47" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="AN47" t="s" s="2">
-        <v>449</v>
+        <v>426</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7484,10 +7518,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7510,16 +7544,16 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>451</v>
+        <v>268</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7545,13 +7579,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>82</v>
+        <v>451</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7569,7 +7603,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7584,16 +7618,16 @@
         <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7601,10 +7635,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7624,18 +7658,20 @@
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7684,7 +7720,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7708,7 +7744,7 @@
         <v>464</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7723,7 +7759,7 @@
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>466</v>
+        <v>82</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7742,17 +7778,15 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>470</v>
-      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7816,13 +7850,13 @@
         <v>104</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>82</v>
@@ -7833,14 +7867,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7856,19 +7890,19 @@
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7918,7 +7952,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7933,7 +7967,7 @@
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>479</v>
@@ -7957,7 +7991,7 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>482</v>
+        <v>82</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7976,7 +8010,7 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>268</v>
+        <v>482</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>483</v>
@@ -7987,9 +8021,7 @@
       <c r="N52" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="O52" t="s" s="2">
-        <v>486</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8013,13 +8045,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>487</v>
+        <v>82</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>488</v>
+        <v>82</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8055,28 +8087,28 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>490</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>82</v>
+        <v>489</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8092,19 +8124,23 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8128,13 +8164,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>82</v>
+        <v>495</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8152,7 +8188,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8167,10 +8203,10 @@
         <v>104</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>495</v>
+        <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>340</v>
+        <v>486</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>496</v>
@@ -8198,7 +8234,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8207,18 +8243,20 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>106</v>
+        <v>499</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>501</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>502</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8273,7 +8311,7 @@
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
@@ -8282,27 +8320,27 @@
         <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>82</v>
+        <v>505</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8313,7 +8351,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8322,20 +8360,18 @@
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>503</v>
+        <v>106</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>506</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8384,13 +8420,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -8399,23 +8435,140 @@
         <v>104</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>507</v>
+        <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AM55" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO55" t="s" s="2">
+      <c r="AM56" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO55">
+  <autoFilter ref="A1:AO56">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8425,7 +8578,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI54">
+  <conditionalFormatting sqref="A2:AI55">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
